--- a/shifts.xlsx
+++ b/shifts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{52D71962-7167-A54E-BD32-088FAAE28EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D258135C-D1AE-A449-B83F-10AEBD4406E3}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{52D71962-7167-A54E-BD32-088FAAE28EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53523EFC-D121-0041-9A8D-BA93A4B14B3D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{F6C4B857-2221-7442-B2F7-99991C74024F}"/>
   </bookViews>
@@ -471,19 +471,25 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
